--- a/tests/A01_pixell_test_plan_bank_account.xlsx
+++ b/tests/A01_pixell_test_plan_bank_account.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>#VALUE!</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Developer:</t>
+  </si>
+  <si>
+    <t>Robinpreet Kaur</t>
   </si>
   <si>
     <t>Class Name:</t>
@@ -1005,7 +1008,9 @@
       <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="D3" s="9"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1014,10 +1019,10 @@
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
       <c r="B4" s="10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="3"/>
@@ -1036,22 +1041,22 @@
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
       <c r="B6" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="31.149999999999995" customFormat="1" s="16">
@@ -1060,19 +1065,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="78" customFormat="1" s="16">
@@ -1081,19 +1086,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="58.5">
@@ -1102,19 +1107,19 @@
         <v>3</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="31.149999999999995" customFormat="1" s="16">
@@ -1123,19 +1128,19 @@
         <v>4</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="31.149999999999995" customFormat="1" s="16">
@@ -1144,16 +1149,16 @@
         <v>5</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="27">
         <v>30355</v>
@@ -1165,16 +1170,16 @@
         <v>6</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>27</v>
-      </c>
       <c r="F12" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="27">
         <v>1050</v>
@@ -1186,16 +1191,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="27">
         <v>6000</v>
@@ -1207,19 +1212,19 @@
         <v>8</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="47.25" customFormat="1" s="16">
@@ -1228,19 +1233,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="31.149999999999995" customFormat="1" s="16">
@@ -1249,19 +1254,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="45.75" customFormat="1" s="16">
@@ -1270,19 +1275,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="32.25" customFormat="1" s="16">
@@ -1291,19 +1296,19 @@
         <v>12</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="45.75">
@@ -1312,19 +1317,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="32.25" customFormat="1" s="16">
@@ -1333,19 +1338,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="32.25" customFormat="1" s="16">
@@ -1354,19 +1359,19 @@
         <v>15</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="16">
@@ -1375,19 +1380,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="16">
@@ -1567,7 +1572,7 @@
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="1"/>
       <c r="B39" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
